--- a/45/Evaluation/Data/Datasheet.xlsx
+++ b/45/Evaluation/Data/Datasheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Moritz/Documents/GitHub/C-Praktikum/45/Evaluation/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C287D90-1342-014E-90A1-8B5B5D8B2F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81B1D6E-AD59-FD48-A71A-14B7EDAB3DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2260" yWindow="2340" windowWidth="27380" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -531,12 +531,17 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="16.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" style="4" customWidth="1"/>
     <col min="5" max="5" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.1640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="15" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="20" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="16.33203125" style="2" bestFit="1" customWidth="1"/>

--- a/45/Evaluation/Data/Datasheet.xlsx
+++ b/45/Evaluation/Data/Datasheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Moritz/Documents/GitHub/C-Praktikum/45/Evaluation/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81B1D6E-AD59-FD48-A71A-14B7EDAB3DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157FC8BD-1C44-D444-8806-5CF6450B1D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2260" yWindow="2340" windowWidth="27380" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17180" yWindow="940" windowWidth="16880" windowHeight="19340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planck" sheetId="1" r:id="rId1"/>
@@ -2234,7 +2234,7 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="C2" s="5">
-        <f t="shared" ref="C2:C24" si="0">B2*0.0005+10*0.00015</f>
+        <f>B2*0.0005+10*0.00015</f>
         <v>1.5001499999999998E-3</v>
       </c>
       <c r="D2" s="5">
@@ -2248,7 +2248,7 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="I2" s="5">
-        <f t="shared" ref="I2:I28" si="1">H2*0.0005+10*0.00015</f>
+        <f t="shared" ref="I2:I28" si="0">H2*0.0005+10*0.00015</f>
         <v>1.5001999999999997E-3</v>
       </c>
       <c r="J2" s="5">
@@ -2262,7 +2262,7 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="N2" s="5">
-        <f t="shared" ref="N2:N31" si="2">M2*0.0005+10*0.00015</f>
+        <f t="shared" ref="N2:N31" si="1">M2*0.0005+10*0.00015</f>
         <v>1.5001999999999997E-3</v>
       </c>
       <c r="O2" s="5">
@@ -2278,7 +2278,7 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="C3" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C2:C24" si="2">B3*0.0005+10*0.00015</f>
         <v>1.5001999999999997E-3</v>
       </c>
       <c r="D3" s="5">
@@ -2292,7 +2292,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5002999999999998E-3</v>
       </c>
       <c r="J3" s="5">
@@ -2306,7 +2306,7 @@
         <v>1E-3</v>
       </c>
       <c r="N3" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.5004999999999999E-3</v>
       </c>
       <c r="O3" s="5">
@@ -2322,7 +2322,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.5002499999999998E-3</v>
       </c>
       <c r="D4" s="5">
@@ -2336,7 +2336,7 @@
         <v>1.9E-3</v>
       </c>
       <c r="I4" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5009499999999998E-3</v>
       </c>
       <c r="J4" s="5">
@@ -2350,7 +2350,7 @@
         <v>2.3E-3</v>
       </c>
       <c r="N4" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.5011499999999997E-3</v>
       </c>
       <c r="O4" s="5">
@@ -2366,7 +2366,7 @@
         <v>3.5999999999999999E-3</v>
       </c>
       <c r="C5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.5017999999999997E-3</v>
       </c>
       <c r="D5" s="5">
@@ -2380,7 +2380,7 @@
         <v>6.4000000000000003E-3</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5031999999999999E-3</v>
       </c>
       <c r="J5" s="5">
@@ -2394,7 +2394,7 @@
         <v>1.0500000000000001E-2</v>
       </c>
       <c r="N5" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.5052499999999999E-3</v>
       </c>
       <c r="O5" s="5">
@@ -2410,7 +2410,7 @@
         <v>1.9800000000000002E-2</v>
       </c>
       <c r="C6" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.5098999999999998E-3</v>
       </c>
       <c r="D6" s="5">
@@ -2424,7 +2424,7 @@
         <v>3.0700000000000002E-2</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5153499999999997E-3</v>
       </c>
       <c r="J6" s="5">
@@ -2438,7 +2438,7 @@
         <v>2.5499999999999998E-2</v>
       </c>
       <c r="N6" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.5127499999999998E-3</v>
       </c>
       <c r="O6" s="5">
@@ -2454,7 +2454,7 @@
         <v>0.309</v>
       </c>
       <c r="C7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.6544999999999997E-3</v>
       </c>
       <c r="D7" s="5">
@@ -2468,7 +2468,7 @@
         <v>0.1615</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5807499999999999E-3</v>
       </c>
       <c r="J7" s="5">
@@ -2482,7 +2482,7 @@
         <v>5.4699999999999999E-2</v>
       </c>
       <c r="N7" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.5273499999999998E-3</v>
       </c>
       <c r="O7" s="5">
@@ -2498,7 +2498,7 @@
         <v>0.81850000000000001</v>
       </c>
       <c r="C8" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.9092499999999999E-3</v>
       </c>
       <c r="D8" s="5">
@@ -2512,7 +2512,7 @@
         <v>0.27400000000000002</v>
       </c>
       <c r="I8" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.6369999999999998E-3</v>
       </c>
       <c r="J8" s="5">
@@ -2526,7 +2526,7 @@
         <v>0.1062</v>
       </c>
       <c r="N8" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.5530999999999997E-3</v>
       </c>
       <c r="O8" s="5">
@@ -2542,7 +2542,7 @@
         <v>1.0041</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.00205E-3</v>
       </c>
       <c r="D9" s="5">
@@ -2556,7 +2556,7 @@
         <v>0.4103</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.7051499999999999E-3</v>
       </c>
       <c r="J9" s="5">
@@ -2570,7 +2570,7 @@
         <v>0.15409999999999999</v>
       </c>
       <c r="N9" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.5770499999999998E-3</v>
       </c>
       <c r="O9" s="5">
@@ -2586,7 +2586,7 @@
         <v>1.391</v>
       </c>
       <c r="C10" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.1955E-3</v>
       </c>
       <c r="D10" s="5">
@@ -2600,7 +2600,7 @@
         <v>0.54479999999999995</v>
       </c>
       <c r="I10" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.7723999999999999E-3</v>
       </c>
       <c r="J10" s="5">
@@ -2614,7 +2614,7 @@
         <v>0.2208</v>
       </c>
       <c r="N10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.6103999999999999E-3</v>
       </c>
       <c r="O10" s="5">
@@ -2630,7 +2630,7 @@
         <v>1.6437999999999999</v>
       </c>
       <c r="C11" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.3219E-3</v>
       </c>
       <c r="D11" s="5">
@@ -2644,7 +2644,7 @@
         <v>0.7419</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.8709499999999997E-3</v>
       </c>
       <c r="J11" s="5">
@@ -2658,7 +2658,7 @@
         <v>0.31459999999999999</v>
       </c>
       <c r="N11" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.6572999999999998E-3</v>
       </c>
       <c r="O11" s="5">
@@ -2674,7 +2674,7 @@
         <v>1.7519</v>
       </c>
       <c r="C12" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.3759499999999999E-3</v>
       </c>
       <c r="D12" s="5">
@@ -2688,7 +2688,7 @@
         <v>0.95860000000000001</v>
       </c>
       <c r="I12" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.9792999999999998E-3</v>
       </c>
       <c r="J12" s="5">
@@ -2702,7 +2702,7 @@
         <v>0.38429999999999997</v>
       </c>
       <c r="N12" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.6921499999999999E-3</v>
       </c>
       <c r="O12" s="5">
@@ -2718,7 +2718,7 @@
         <v>2.1909999999999998</v>
       </c>
       <c r="C13" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.5954999999999997E-3</v>
       </c>
       <c r="D13" s="5">
@@ -2732,7 +2732,7 @@
         <v>1.2890999999999999</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.1445499999999998E-3</v>
       </c>
       <c r="J13" s="5">
@@ -2746,7 +2746,7 @@
         <v>0.47360000000000002</v>
       </c>
       <c r="N13" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.7367999999999997E-3</v>
       </c>
       <c r="O13" s="5">
@@ -2762,7 +2762,7 @@
         <v>2.7256</v>
       </c>
       <c r="C14" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.8627999999999995E-3</v>
       </c>
       <c r="D14" s="5">
@@ -2776,7 +2776,7 @@
         <v>1.4906999999999999</v>
       </c>
       <c r="I14" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.2453499999999997E-3</v>
       </c>
       <c r="J14" s="5">
@@ -2790,7 +2790,7 @@
         <v>0.63590000000000002</v>
       </c>
       <c r="N14" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.8179499999999998E-3</v>
       </c>
       <c r="O14" s="5">
@@ -2806,7 +2806,7 @@
         <v>3.3475999999999999</v>
       </c>
       <c r="C15" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.1738000000000001E-3</v>
       </c>
       <c r="D15" s="5">
@@ -2820,7 +2820,7 @@
         <v>1.9239999999999999</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.4619999999999998E-3</v>
       </c>
       <c r="J15" s="5">
@@ -2834,7 +2834,7 @@
         <v>0.71020000000000005</v>
       </c>
       <c r="N15" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.8550999999999997E-3</v>
       </c>
       <c r="O15" s="5">
@@ -2850,7 +2850,7 @@
         <v>4.0389999999999997</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.5195000000000001E-3</v>
       </c>
       <c r="D16" s="5">
@@ -2864,7 +2864,7 @@
         <v>2.1585999999999999</v>
       </c>
       <c r="I16" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.5792999999999996E-3</v>
       </c>
       <c r="J16" s="5">
@@ -2878,7 +2878,7 @@
         <v>0.88100000000000001</v>
       </c>
       <c r="N16" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.9405E-3</v>
       </c>
       <c r="O16" s="5">
@@ -2894,7 +2894,7 @@
         <v>4.3343999999999996</v>
       </c>
       <c r="C17" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.6671999999999998E-3</v>
       </c>
       <c r="D17" s="5">
@@ -2908,7 +2908,7 @@
         <v>2.585</v>
       </c>
       <c r="I17" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.7924999999999998E-3</v>
       </c>
       <c r="J17" s="5">
@@ -2922,7 +2922,7 @@
         <v>1.0257000000000001</v>
       </c>
       <c r="N17" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.0128500000000001E-3</v>
       </c>
       <c r="O17" s="5">
@@ -2938,7 +2938,7 @@
         <v>4.5881999999999996</v>
       </c>
       <c r="C18" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.7940999999999999E-3</v>
       </c>
       <c r="D18" s="5">
@@ -2952,7 +2952,7 @@
         <v>3.1669999999999998</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.0834999999999994E-3</v>
       </c>
       <c r="J18" s="5">
@@ -2966,7 +2966,7 @@
         <v>1.2095</v>
       </c>
       <c r="N18" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.1047499999999999E-3</v>
       </c>
       <c r="O18" s="5">
@@ -2982,7 +2982,7 @@
         <v>5.4409999999999998</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4.2204999999999994E-3</v>
       </c>
       <c r="D19" s="5">
@@ -2996,7 +2996,7 @@
         <v>3.5548999999999999</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.2774499999999999E-3</v>
       </c>
       <c r="J19" s="5">
@@ -3010,7 +3010,7 @@
         <v>1.4865999999999999</v>
       </c>
       <c r="N19" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.2432999999999997E-3</v>
       </c>
       <c r="O19" s="5">
@@ -3026,7 +3026,7 @@
         <v>6.4108999999999998</v>
       </c>
       <c r="C20" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4.7054499999999999E-3</v>
       </c>
       <c r="D20" s="5">
@@ -3040,7 +3040,7 @@
         <v>3.8980000000000001</v>
       </c>
       <c r="I20" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.4489999999999998E-3</v>
       </c>
       <c r="J20" s="5">
@@ -3054,7 +3054,7 @@
         <v>1.7848999999999999</v>
       </c>
       <c r="N20" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.39245E-3</v>
       </c>
       <c r="O20" s="5">
@@ -3070,7 +3070,7 @@
         <v>7.1855000000000002</v>
       </c>
       <c r="C21" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5.0927500000000001E-3</v>
       </c>
       <c r="D21" s="5">
@@ -3084,7 +3084,7 @@
         <v>4.1425999999999998</v>
       </c>
       <c r="I21" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.5712999999999995E-3</v>
       </c>
       <c r="J21" s="5">
@@ -3098,7 +3098,7 @@
         <v>2.2917000000000001</v>
       </c>
       <c r="N21" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.6458499999999999E-3</v>
       </c>
       <c r="O21" s="5">
@@ -3114,7 +3114,7 @@
         <v>8.1320999999999994</v>
       </c>
       <c r="C22" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5.5660499999999995E-3</v>
       </c>
       <c r="D22" s="5">
@@ -3128,7 +3128,7 @@
         <v>4.8513000000000002</v>
       </c>
       <c r="I22" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.9256500000000001E-3</v>
       </c>
       <c r="J22" s="5">
@@ -3142,7 +3142,7 @@
         <v>2.7991000000000001</v>
       </c>
       <c r="N22" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.8995499999999999E-3</v>
       </c>
       <c r="O22" s="5">
@@ -3158,7 +3158,7 @@
         <v>9.0862999999999996</v>
       </c>
       <c r="C23" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6.0431499999999997E-3</v>
       </c>
       <c r="D23" s="5">
@@ -3172,7 +3172,7 @@
         <v>5.298</v>
       </c>
       <c r="I23" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4.1489999999999999E-3</v>
       </c>
       <c r="J23" s="5">
@@ -3186,7 +3186,7 @@
         <v>3.2469000000000001</v>
       </c>
       <c r="N23" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.1234499999999998E-3</v>
       </c>
       <c r="O23" s="5">
@@ -3202,7 +3202,7 @@
         <v>9.8714999999999993</v>
       </c>
       <c r="C24" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6.4357499999999996E-3</v>
       </c>
       <c r="D24" s="5">
@@ -3216,7 +3216,7 @@
         <v>6.3129</v>
       </c>
       <c r="I24" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4.6564499999999995E-3</v>
       </c>
       <c r="J24" s="5">
@@ -3230,7 +3230,7 @@
         <v>3.9178000000000002</v>
       </c>
       <c r="N24" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.4589E-3</v>
       </c>
       <c r="O24" s="5">
@@ -3260,7 +3260,7 @@
         <v>7.0701000000000001</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.0350500000000001E-3</v>
       </c>
       <c r="J25" s="5">
@@ -3274,7 +3274,7 @@
         <v>4.5316999999999998</v>
       </c>
       <c r="N25" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.7658499999999994E-3</v>
       </c>
       <c r="O25" s="5">
@@ -3290,7 +3290,7 @@
         <v>8.0295000000000005</v>
       </c>
       <c r="I26" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.5147499999999997E-3</v>
       </c>
       <c r="J26" s="5">
@@ -3304,7 +3304,7 @@
         <v>5.7384000000000004</v>
       </c>
       <c r="N26" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.3692000000000002E-3</v>
       </c>
       <c r="O26" s="5">
@@ -3320,7 +3320,7 @@
         <v>9.2333999999999996</v>
       </c>
       <c r="I27" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.1166999999999992E-3</v>
       </c>
       <c r="J27" s="5">
@@ -3334,7 +3334,7 @@
         <v>6.2610000000000001</v>
       </c>
       <c r="N27" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.6305000000000001E-3</v>
       </c>
       <c r="O27" s="5">
@@ -3350,7 +3350,7 @@
         <v>9.9552999999999994</v>
       </c>
       <c r="I28" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.4776499999999997E-3</v>
       </c>
       <c r="J28" s="5">
@@ -3364,7 +3364,7 @@
         <v>7.069</v>
       </c>
       <c r="N28" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5.0344999999999999E-3</v>
       </c>
       <c r="O28" s="5">
@@ -3380,7 +3380,7 @@
         <v>7.9612999999999996</v>
       </c>
       <c r="N29" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5.4806499999999992E-3</v>
       </c>
       <c r="O29" s="5">
@@ -3396,7 +3396,7 @@
         <v>8.5769000000000002</v>
       </c>
       <c r="N30" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5.7884499999999997E-3</v>
       </c>
       <c r="O30" s="5">
@@ -3412,7 +3412,7 @@
         <v>9.9870000000000001</v>
       </c>
       <c r="N31" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6.4935000000000001E-3</v>
       </c>
       <c r="O31" s="5">
@@ -3422,5 +3422,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/45/Evaluation/Data/Datasheet.xlsx
+++ b/45/Evaluation/Data/Datasheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Moritz/Documents/GitHub/C-Praktikum/45/Evaluation/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157FC8BD-1C44-D444-8806-5CF6450B1D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550D06A8-60A8-FC4F-910F-725E28A99BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17180" yWindow="940" windowWidth="16880" windowHeight="19340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>I (T=120 C)</t>
-  </si>
-  <si>
-    <t>Error I (T=120C)</t>
   </si>
   <si>
     <t>Error U (T=120 C)</t>
@@ -136,6 +133,9 @@
   </si>
   <si>
     <t>U (578nm)</t>
+  </si>
+  <si>
+    <t>Error I (T=120 C)</t>
   </si>
 </sst>
 </file>
@@ -551,67 +551,67 @@
   <sheetData>
     <row r="1" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2181,7 +2181,8 @@
     <col min="7" max="8" width="15.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="15.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.1640625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="17.83203125" style="4" customWidth="1"/>
     <col min="16" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
@@ -2220,10 +2221,10 @@
         <v>10</v>
       </c>
       <c r="N1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2278,7 +2279,7 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="C3" s="5">
-        <f t="shared" ref="C2:C24" si="2">B3*0.0005+10*0.00015</f>
+        <f t="shared" ref="C3:C24" si="2">B3*0.0005+10*0.00015</f>
         <v>1.5001999999999997E-3</v>
       </c>
       <c r="D3" s="5">
